--- a/Testing Data/Bi-directional Specimen Testing.xlsx
+++ b/Testing Data/Bi-directional Specimen Testing.xlsx
@@ -662,10 +662,18 @@
       <c r="H5" s="16"/>
       <c r="I5" s="15"/>
       <c r="J5" s="16"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="17"/>
+      <c r="K5" s="15" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="L5" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>82.5</v>
+      </c>
       <c r="P5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
